--- a/Pulse_Auto_Map.xlsx
+++ b/Pulse_Auto_Map.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Пакет команд бота: /start, /help, /menu, системные команды.</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,8 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Модерация заявок на вступление и админ-действия над участниками:
+одобрение/отклонение анкет, мут, бан, чёрный список, восстановление досье.</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1679,9 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>FSM-сценарий регистрации новых участников: пошаговая анкета
+(имя, возраст, город, реф-код), валидация, защита от повторов,
+генерация invite-ссылки.</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1921,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Пакет логики обработки сообщений: майнинг, реакции, штрафы, события чата.</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2324,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>AdminDashboard — корневой компонент админ-панели Puls Chat. Сайдбар + навигация по разделам (Новости/Модули/Статистика/Журнал/ Триггеры/Пресс-релизы/Шиппер/Экономика/Система/Права). Хранит массив UPDATES — данные для дерева Новостей.</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2368,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>PostCSS-конфиг сайта: подключает Tailwind и autoprefixer.</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2434,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomySubTable — под-таблица параметров одной подкатегории Экономики (legacy табличный вид).</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2456,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomyEditForm — inline-форма редактирования значения параметра экономики (новое значение + обязательная причина-комментарий).</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2478,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomyMiniChart — мини-график истории изменений значения параметра (для popover/inline-инспектора в строках Экономики).</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2522,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomyToggleForm — inline-форма подтверждения вкл/выкл параметра экономики (с обязательной причиной-комментарием в журнал).</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2544,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomyCancelPointwiseModal — модалка точечной отмены по ID транзакции.</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2632,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomyEditModal — модальная версия формы редактирования параметра экономики (legacy; в новых карточках используется inline-EditForm).</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2654,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomyCategory — карточка категории Экономики (legacy-табличный вид до перехода на карточки-модули V1.17.0h2b).</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2698,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomyCancelMassModal — модалка «Массовая отмена выплат» (откат начислений по периоду и категории).</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2720,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>Хук useEconomyWS — подключение к WebSocket экономики (живые апдейты значений параметров и тумблеров).</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2742,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>EconomyToggleModal — модальная версия формы подтверждения вкл/выкл параметра экономики (legacy; в новых карточках inline-ToggleForm).</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3138,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>PressReleasePage — страница раздела «Пресс-релизы»: список (PressReleaseList) → редактор (PressReleaseEditor) → предпросмотр и планировщик публикаций.</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3160,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>PressReleaseList — список пресс-релизов с фильтрами по статусу (черновик/запланирован/опубликован) и кнопкой создания нового.</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3204,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено.</t>
+          <t>DateTimePicker — общий компонент выбора даты и времени. Используется в Пресс-релизах для назначения времени публикации.</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3809,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Генератор записей релиз-нотов для CHANGELOG.md (вспомогательный инструмент).</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3882,7 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Утилита: скачивание/локальная копия БД бота (вспомогательный скрипт).</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3904,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Утилита-проверялка постов в БД (диагностика, разовый запуск).</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4068,7 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Утилита: копирование ассетов-баннеров в нужную папку (разовая операция).</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4140,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Утилита-помощник разрешения git-конфликтов (вспомогательный скрипт).</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4237,7 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Утилита-проверялка списка топиков чата (диагностика, разовый запуск).</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4259,7 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Утилита-хотфикс данных пользователя в БД (ручная операция).</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4385,7 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Пакет ядра бота: module_guard (тумблеры модулей), ws_role/ws_resolver (роли и чаты сообществ).</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5525,7 @@
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты API тумблеров модулей (/api/modules/*).</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5719,7 @@
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты ws_resolver — резолв workspace_id по chat_id / thread_id.</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5809,7 @@
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты module_guard (is_module_enabled / гарды модулей в боте).</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5975,7 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты миграций connect-flow (composite PK, схема таблиц подключения).</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5997,7 @@
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты DB-слоя module_toggles (get/set/upsert тумблеров).</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6019,7 @@
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты shop_mechanics — внутриботная логика магазина.</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6041,7 @@
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты lifecycle подключения бота к чату (Подпроект #2 connect-flow).</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6063,7 @@
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты миграции бэкфилла module_toggles (V1.17.0h0b/h3).</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6175,7 @@
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты консолидации workspace-ов (объединение ws5/ws6 в ws1).</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6225,7 @@
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Тесты миграции ws_runtime_seed (стартовые данные workspace из .env).</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6611,9 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>FastAPI-приложение Puls Chat — основной HTTP/WS API сайта.
+Аутентификация (Telegram), endpoints для чатов/админов/статистики/
+триггеров/пресс-релизов/титулов; подключает economy_router и WS-канал.</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6750,7 @@
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Описание в коде не найдено. Добавьте """описание""" в начало файла.</t>
+          <t>Пакет API-роутеров (economy_routes, economy_ws и др.) — подключаются в api.py.</t>
         </is>
       </c>
     </row>
